--- a/SuppXLS/Scen_UC_ELC_ELCBHEAT_10_20.xlsx
+++ b/SuppXLS/Scen_UC_ELC_ELCBHEAT_10_20.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403DE500-4E88-41AE-8E96-2C0097FACF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
   </bookViews>
   <sheets>
     <sheet name="ELC_BHEAT_10_20" sheetId="1" r:id="rId1"/>
